--- a/resources/templates/karaba/deregistration_application.xlsx
+++ b/resources/templates/karaba/deregistration_application.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="58">
   <si>
     <r>
       <t xml:space="preserve">■ 자동차등록규칙 [별지 제17호서식] (앞 쪽)</t>
@@ -287,6 +287,15 @@
     <r>
       <t xml:space="preserve">수임자</t>
     </r>
+  </si>
+  <si>
+    <t>경기도 고양시 덕양구 유산길 9, 203호(내유동)</t>
+  </si>
+  <si>
+    <t>길영채</t>
+  </si>
+  <si>
+    <t>11-95-278048-01</t>
   </si>
 </sst>
 </file>
@@ -497,10 +506,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4B184"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="63">
@@ -1375,260 +1381,260 @@
     <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="18" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="7" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="19" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="3" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="19" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="3" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="20" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="21" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="22" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="23" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="24" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="19" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="25" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="26" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="3" borderId="25" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="27" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="4" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="28" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="164" fillId="3" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="18" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="7" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="49" fillId="0" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="29" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="30" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="3" borderId="31" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="32" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="34" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="35" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="36" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="27" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="37" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="38" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="39" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="26" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="3" borderId="40" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="30" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="41" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="3" borderId="42" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="14" numFmtId="165" fillId="3" borderId="43" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="15" numFmtId="165" fillId="0" borderId="35" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="20" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="24" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="45" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="13" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="47" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="15" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="11" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="44" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="16" numFmtId="0" fillId="0" borderId="50" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="51" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="52" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="53" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="35" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="54" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="19" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="13" numFmtId="14" fillId="3" borderId="19" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="55" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="56" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="57" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="17" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="58" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="59" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="60" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="28" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="61" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="19" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="58" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="9" numFmtId="166" fillId="0" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="4" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="62" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="60" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="9" numFmtId="0" fillId="4" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="18" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="7" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="19" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="3" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="19" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="3" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="20" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="21" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="22" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="23" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="24" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="19" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="25" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="26" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="12" numFmtId="0" fillId="3" borderId="25" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="27" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="4" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="28" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="12" numFmtId="164" fillId="3" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="18" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="7" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="49" fillId="0" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="29" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="30" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="12" numFmtId="0" fillId="3" borderId="31" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="32" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="34" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="35" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="36" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="27" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="37" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="38" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="39" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="26" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="12" numFmtId="0" fillId="3" borderId="40" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="30" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="41" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="3" borderId="42" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="14" numFmtId="165" fillId="3" borderId="43" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="15" numFmtId="165" fillId="0" borderId="35" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="44" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="20" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="24" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="45" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="46" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="13" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="47" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="15" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="11" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="49" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="44" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="16" numFmtId="0" fillId="0" borderId="50" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="51" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="0" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="52" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="53" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="35" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="54" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="19" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="13" numFmtId="14" fillId="3" borderId="19" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="55" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="56" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="57" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="17" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="58" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="59" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="60" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="28" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="61" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="19" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="58" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="9" numFmtId="166" fillId="0" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="4" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="9" numFmtId="166" fillId="4" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="62" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="60" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1987,7 +1993,7 @@
     <col min="17" max="17" width="9" customWidth="true" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16144" customHeight="1" ht="16.5" s="32" customFormat="1">
+    <row r="1" spans="1:17" customHeight="1" ht="16.5" s="31" customFormat="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
           <r>
@@ -1995,16 +2001,16 @@
           </r>
         </is>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
       <c r="L1" s="10" t="inlineStr">
         <is>
           <r>
@@ -2012,7 +2018,7 @@
           </r>
         </is>
       </c>
-      <c r="M1" s="34"/>
+      <c r="M1" s="33"/>
       <c r="N1" s="11" t="inlineStr">
         <is>
           <r>
@@ -2021,21 +2027,21 @@
         </is>
       </c>
     </row>
-    <row r="2" spans="1:16144" customHeight="1" ht="38.25" s="32" customFormat="1">
-      <c r="A2" s="35" t="inlineStr">
+    <row r="2" spans="1:17" customHeight="1" ht="38.25" s="31" customFormat="1">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">자동차말소등록신청서</t>
           </r>
         </is>
       </c>
-      <c r="M2" s="36"/>
-    </row>
-    <row r="3" spans="1:16144" customHeight="1" ht="17.25" s="32" customFormat="1">
-      <c r="A3" s="37"/>
-      <c r="M3" s="38"/>
-    </row>
-    <row r="4" spans="1:16144" customHeight="1" ht="26.25" s="32" customFormat="1">
+      <c r="M2" s="35"/>
+    </row>
+    <row r="3" spans="1:17" customHeight="1" ht="17.25" s="31" customFormat="1">
+      <c r="A3" s="36"/>
+      <c r="M3" s="37"/>
+    </row>
+    <row r="4" spans="1:17" customHeight="1" ht="26.25" s="31" customFormat="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <r>
@@ -2044,72 +2050,72 @@
         </is>
       </c>
       <c r="B4" s="12"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="40" t="inlineStr">
+      <c r="C4" s="38"/>
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">접수일</t>
           </r>
         </is>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="40" t="inlineStr">
+      <c r="E4" s="38"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="39" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">발급일</t>
           </r>
         </is>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="42" t="inlineStr">
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="41" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">처리기간        즉시</t>
           </r>
         </is>
       </c>
-      <c r="L4" s="39"/>
-      <c r="M4" s="43"/>
-    </row>
-    <row r="5" spans="1:16144" customHeight="1" ht="19.5" s="32" customFormat="1">
-      <c r="A5" s="44"/>
-      <c r="M5" s="38"/>
-    </row>
-    <row r="6" spans="1:16144" customHeight="1" ht="40.5" s="32" customFormat="1">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="L4" s="38"/>
+      <c r="M4" s="42"/>
+    </row>
+    <row r="5" spans="1:17" customHeight="1" ht="19.5" s="31" customFormat="1">
+      <c r="A5" s="43"/>
+      <c r="M5" s="37"/>
+    </row>
+    <row r="6" spans="1:17" customHeight="1" ht="40.5" s="31" customFormat="1">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">소유자</t>
           </r>
         </is>
       </c>
-      <c r="B6" s="46" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">성명(명칭)</t>
           </r>
         </is>
       </c>
-      <c r="C6" s="47"/>
-      <c r="D6" s="48" t="inlineStr">
+      <c r="C6" s="46"/>
+      <c r="D6" s="47" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">김태균(상품용)</t>
           </r>
         </is>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="47"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="46"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
           <r>
@@ -2118,8 +2124,8 @@
         </is>
       </c>
     </row>
-    <row r="7" spans="1:16144" customHeight="1" ht="40.5" s="32" customFormat="1">
-      <c r="A7" s="50"/>
+    <row r="7" spans="1:17" customHeight="1" ht="40.5" s="31" customFormat="1">
+      <c r="A7" s="49"/>
       <c r="B7" s="13" t="inlineStr">
         <is>
           <r>
@@ -2127,20 +2133,20 @@
           </r>
         </is>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52" t="inlineStr">
+      <c r="C7" s="50"/>
+      <c r="D7" s="51" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">740427-1067326</t>
           </r>
         </is>
       </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="54"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="53"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
           <r>
@@ -2148,11 +2154,11 @@
           </r>
         </is>
       </c>
-      <c r="L7" s="55"/>
-      <c r="M7" s="54"/>
-    </row>
-    <row r="8" spans="1:16144" customHeight="1" ht="50.25" s="32" customFormat="1">
-      <c r="A8" s="56"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="53"/>
+    </row>
+    <row r="8" spans="1:17" customHeight="1" ht="50.25" s="31" customFormat="1">
+      <c r="A8" s="55"/>
       <c r="B8" s="14" t="inlineStr">
         <is>
           <r>
@@ -2160,100 +2166,100 @@
           </r>
         </is>
       </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="58" t="inlineStr">
+      <c r="C8" s="56"/>
+      <c r="D8" s="57" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">경기도 부천시 오정구 송내대로 450, 207호(삼정동, 국민차매매단지)</t>
           </r>
         </is>
       </c>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="59"/>
-    </row>
-    <row r="9" spans="1:16144" customHeight="1" ht="20.25" s="32" customFormat="1">
-      <c r="A9" s="60"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="61"/>
-      <c r="M9" s="62"/>
-    </row>
-    <row r="10" spans="1:16144" customHeight="1" ht="17.25" s="32" customFormat="1">
-      <c r="A10" s="63" t="inlineStr">
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="58"/>
+    </row>
+    <row r="9" spans="1:17" customHeight="1" ht="20.25" s="31" customFormat="1">
+      <c r="A9" s="59"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="61"/>
+    </row>
+    <row r="10" spans="1:17" customHeight="1" ht="17.25" s="31" customFormat="1">
+      <c r="A10" s="62" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">자동차등록번호</t>
           </r>
         </is>
       </c>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="66" t="inlineStr">
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="65" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">차대번호</t>
           </r>
         </is>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="67" t="inlineStr">
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="66" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">주행거리 </t>
           </r>
         </is>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="64"/>
-      <c r="M10" s="68"/>
-    </row>
-    <row r="11" spans="1:16144" customHeight="1" ht="40.5" s="32" customFormat="1">
-      <c r="A11" s="69" t="inlineStr">
+      <c r="K10" s="63"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="67"/>
+    </row>
+    <row r="11" spans="1:17" customHeight="1" ht="40.5" s="31" customFormat="1">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">135수6617</t>
           </r>
         </is>
       </c>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="72" t="inlineStr">
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="71" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">WVWZZZ3HZKE022850</t>
           </r>
         </is>
       </c>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="73">
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="72">
         <v>175438</v>
       </c>
-      <c r="K11" s="70"/>
-      <c r="L11" s="70"/>
-      <c r="M11" s="74" t="inlineStr">
+      <c r="K11" s="69"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="73" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">km</t>
@@ -2261,23 +2267,23 @@
         </is>
       </c>
     </row>
-    <row r="12" spans="1:16144" customHeight="1" ht="18" s="32" customFormat="1">
-      <c r="A12" s="75"/>
-      <c r="B12" s="76"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="76"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="76"/>
-      <c r="M12" s="77"/>
-    </row>
-    <row r="13" spans="1:16144" customHeight="1" ht="24" s="32" customFormat="1">
-      <c r="A13" s="78" t="inlineStr">
+    <row r="12" spans="1:17" customHeight="1" ht="18" s="31" customFormat="1">
+      <c r="A12" s="74"/>
+      <c r="B12" s="75"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="75"/>
+      <c r="L12" s="75"/>
+      <c r="M12" s="76"/>
+    </row>
+    <row r="13" spans="1:17" customHeight="1" ht="24" s="31" customFormat="1">
+      <c r="A13" s="77" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록의 원인</t>
@@ -2291,12 +2297,12 @@
           </r>
         </is>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="78"/>
       <c r="I13" s="18" t="inlineStr">
         <is>
           <r>
@@ -2304,13 +2310,13 @@
           </r>
         </is>
       </c>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="80"/>
-    </row>
-    <row r="14" spans="1:16144" customHeight="1" ht="24" s="32" customFormat="1">
-      <c r="A14" s="81"/>
+      <c r="J13" s="78"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="78"/>
+      <c r="M13" s="79"/>
+    </row>
+    <row r="14" spans="1:17" customHeight="1" ht="24" s="31" customFormat="1">
+      <c r="A14" s="80"/>
       <c r="B14" s="19" t="inlineStr">
         <is>
           <r>
@@ -2318,12 +2324,12 @@
           </r>
         </is>
       </c>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="82"/>
-      <c r="H14" s="82"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
       <c r="I14" s="20" t="inlineStr">
         <is>
           <r>
@@ -2331,13 +2337,13 @@
           </r>
         </is>
       </c>
-      <c r="J14" s="82"/>
-      <c r="K14" s="82"/>
-      <c r="L14" s="82"/>
-      <c r="M14" s="83"/>
-    </row>
-    <row r="15" spans="1:16144" customHeight="1" ht="24" s="32" customFormat="1">
-      <c r="A15" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="82"/>
+    </row>
+    <row r="15" spans="1:17" customHeight="1" ht="24" s="31" customFormat="1">
+      <c r="A15" s="80"/>
       <c r="B15" s="19" t="inlineStr">
         <is>
           <r>
@@ -2345,12 +2351,12 @@
           </r>
         </is>
       </c>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="82"/>
-      <c r="H15" s="82"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
       <c r="I15" s="20" t="inlineStr">
         <is>
           <r>
@@ -2358,13 +2364,13 @@
           </r>
         </is>
       </c>
-      <c r="J15" s="82"/>
-      <c r="K15" s="82"/>
-      <c r="L15" s="82"/>
-      <c r="M15" s="83"/>
-    </row>
-    <row r="16" spans="1:16144" customHeight="1" ht="24" s="32" customFormat="1">
-      <c r="A16" s="81"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="82"/>
+    </row>
+    <row r="16" spans="1:17" customHeight="1" ht="24" s="31" customFormat="1">
+      <c r="A16" s="80"/>
       <c r="B16" s="19" t="inlineStr">
         <is>
           <r>
@@ -2372,12 +2378,12 @@
           </r>
         </is>
       </c>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
       <c r="I16" s="20" t="inlineStr">
         <is>
           <r>
@@ -2385,13 +2391,13 @@
           </r>
         </is>
       </c>
-      <c r="J16" s="82"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="83"/>
-    </row>
-    <row r="17" spans="1:16144" customHeight="1" ht="24" s="32" customFormat="1">
-      <c r="A17" s="81"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="82"/>
+    </row>
+    <row r="17" spans="1:17" customHeight="1" ht="24" s="31" customFormat="1">
+      <c r="A17" s="80"/>
       <c r="B17" s="19" t="inlineStr">
         <is>
           <r>
@@ -2399,12 +2405,12 @@
           </r>
         </is>
       </c>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="82"/>
-      <c r="H17" s="82"/>
+      <c r="C17" s="81"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
       <c r="I17" s="20" t="inlineStr">
         <is>
           <r>
@@ -2412,13 +2418,13 @@
           </r>
         </is>
       </c>
-      <c r="J17" s="82"/>
-      <c r="K17" s="82"/>
-      <c r="L17" s="82"/>
-      <c r="M17" s="83"/>
-    </row>
-    <row r="18" spans="1:16144" customHeight="1" ht="24" s="32" customFormat="1">
-      <c r="A18" s="84"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="81"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="82"/>
+    </row>
+    <row r="18" spans="1:17" customHeight="1" ht="24" s="31" customFormat="1">
+      <c r="A18" s="83"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
           <r>
@@ -2426,12 +2432,12 @@
           </r>
         </is>
       </c>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
       <c r="I18" s="22" t="inlineStr">
         <is>
           <r>
@@ -2439,27 +2445,27 @@
           </r>
         </is>
       </c>
-      <c r="J18" s="85"/>
-      <c r="K18" s="85"/>
-      <c r="L18" s="85"/>
-      <c r="M18" s="86"/>
-    </row>
-    <row r="19" spans="1:16144" customHeight="1" ht="17.25" s="32" customFormat="1">
-      <c r="A19" s="87"/>
-      <c r="B19" s="76"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="77"/>
-    </row>
-    <row r="20" spans="1:16144">
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="85"/>
+    </row>
+    <row r="19" spans="1:17" customHeight="1" ht="17.25" s="31" customFormat="1">
+      <c r="A19" s="86"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="75"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="75"/>
+      <c r="J19" s="75"/>
+      <c r="K19" s="75"/>
+      <c r="L19" s="75"/>
+      <c r="M19" s="76"/>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <r>
@@ -2467,32 +2473,32 @@
           </r>
         </is>
       </c>
-      <c r="B20" s="88" t="inlineStr">
+      <c r="B20" s="87" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">[ V]발급 필요</t>
           </r>
         </is>
       </c>
-      <c r="C20" s="89"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="90" t="inlineStr">
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="89" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">[ ]발급 불필요</t>
           </r>
         </is>
       </c>
-      <c r="J20" s="89"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="89"/>
-      <c r="M20" s="91"/>
-    </row>
-    <row r="21" spans="1:16144" customHeight="1" ht="17.25" s="32" customFormat="1">
+      <c r="J20" s="88"/>
+      <c r="K20" s="88"/>
+      <c r="L20" s="88"/>
+      <c r="M20" s="90"/>
+    </row>
+    <row r="21" spans="1:17" customHeight="1" ht="17.25" s="31" customFormat="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <r>
@@ -2500,52 +2506,52 @@
           </r>
         </is>
       </c>
-      <c r="B21" s="92"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="61"/>
-      <c r="L21" s="61"/>
-      <c r="M21" s="93"/>
-    </row>
-    <row r="22" spans="1:16144" customHeight="1" ht="17.25" s="32" customFormat="1">
-      <c r="A22" s="94"/>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="89"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="89"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="89"/>
-      <c r="L22" s="89"/>
-      <c r="M22" s="91"/>
-    </row>
-    <row r="23" spans="1:16144">
-      <c r="A23" s="95" t="inlineStr">
+      <c r="B21" s="91"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="92"/>
+    </row>
+    <row r="22" spans="1:17" customHeight="1" ht="17.25" s="31" customFormat="1">
+      <c r="A22" s="93"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="88"/>
+      <c r="K22" s="88"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="90"/>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="94" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">「자동차관리법」 제13조제1항, 「자동차등록령」 제31조제1항 및 「자동차등록규칙」 제37조에 따라 자동차말소등록을 신청합니다.</t>
           </r>
         </is>
       </c>
-      <c r="M23" s="36"/>
-    </row>
-    <row r="24" spans="1:16144" customHeight="1" ht="26.25" s="32" customFormat="1">
-      <c r="A24" s="96" t="str">
+      <c r="M23" s="35"/>
+    </row>
+    <row r="24" spans="1:17" customHeight="1" ht="26.25" s="31" customFormat="1">
+      <c r="A24" s="95" t="str">
         <f>TODAY()</f>
         <v>0</v>
       </c>
-      <c r="M24" s="36"/>
-    </row>
-    <row r="25" spans="1:16144" customHeight="1" ht="23.25" s="32" customFormat="1">
+      <c r="M24" s="35"/>
+    </row>
+    <row r="25" spans="1:17" customHeight="1" ht="23.25" s="31" customFormat="1">
       <c r="A25" s="23"/>
       <c r="C25" s="24"/>
       <c r="D25" s="25"/>
@@ -2557,9 +2563,9 @@
         </is>
       </c>
       <c r="H25" s="26"/>
-      <c r="M25" s="36"/>
-    </row>
-    <row r="26" spans="1:16144" customHeight="1" ht="23.25" s="32" customFormat="1">
+      <c r="M25" s="35"/>
+    </row>
+    <row r="26" spans="1:17" customHeight="1" ht="23.25" s="31" customFormat="1">
       <c r="A26" s="23"/>
       <c r="C26" s="24"/>
       <c r="D26" s="25" t="inlineStr">
@@ -2580,7 +2586,7 @@
       <c r="K26" s="25"/>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:16144" customHeight="1" ht="23.25" s="32" customFormat="1">
+    <row r="27" spans="1:17" customHeight="1" ht="23.25" s="31" customFormat="1">
       <c r="A27" s="23"/>
       <c r="C27" s="24"/>
       <c r="D27" s="25"/>
@@ -2593,16 +2599,16 @@
       </c>
       <c r="H27" s="25"/>
       <c r="K27" s="25"/>
-      <c r="L27" s="97" t="inlineStr">
+      <c r="L27" s="96" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">(서명 또는 인)</t>
           </r>
         </is>
       </c>
-      <c r="M27" s="36"/>
-    </row>
-    <row r="28" spans="1:16144" customHeight="1" ht="17.25" s="32" customFormat="1">
+      <c r="M27" s="35"/>
+    </row>
+    <row r="28" spans="1:17" customHeight="1" ht="17.25" s="31" customFormat="1">
       <c r="A28" s="23"/>
       <c r="B28" s="24"/>
       <c r="C28" s="24"/>
@@ -2617,28 +2623,28 @@
       <c r="L28" s="25"/>
       <c r="M28" s="27"/>
     </row>
-    <row r="29" spans="1:16144" customHeight="1" ht="24" s="32" customFormat="1">
-      <c r="A29" s="98" t="inlineStr">
+    <row r="29" spans="1:17" customHeight="1" ht="24" s="31" customFormat="1">
+      <c r="A29" s="97" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">특별시장ㆍ광역시장ㆍ도지사ㆍ 특별자치도지사 또는 시장ㆍ군수ㆍ구청장 귀하</t>
           </r>
         </is>
       </c>
-      <c r="B29" s="99"/>
-      <c r="C29" s="99"/>
-      <c r="D29" s="99"/>
-      <c r="E29" s="99"/>
-      <c r="F29" s="99"/>
-      <c r="G29" s="99"/>
-      <c r="H29" s="99"/>
-      <c r="I29" s="99"/>
-      <c r="J29" s="99"/>
-      <c r="K29" s="99"/>
-      <c r="L29" s="99"/>
-      <c r="M29" s="100"/>
-    </row>
-    <row r="30" spans="1:16144" customHeight="1" ht="20.25" s="32" customFormat="1">
+      <c r="B29" s="98"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="98"/>
+      <c r="H29" s="98"/>
+      <c r="I29" s="98"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="98"/>
+      <c r="L29" s="98"/>
+      <c r="M29" s="99"/>
+    </row>
+    <row r="30" spans="1:17" customHeight="1" ht="20.25" s="31" customFormat="1">
       <c r="A30" s="5"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2653,7 +2659,7 @@
       <c r="L30" s="6"/>
       <c r="M30" s="7"/>
     </row>
-    <row r="31" spans="1:16144" customHeight="1" ht="19.5" s="32" customFormat="1">
+    <row r="31" spans="1:17" customHeight="1" ht="19.5" s="31" customFormat="1">
       <c r="A31" s="5"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2668,49 +2674,49 @@
       <c r="L31" s="6"/>
       <c r="M31" s="7"/>
     </row>
-    <row r="32" spans="1:16144" customHeight="1" ht="31.5" s="32" customFormat="1">
-      <c r="A32" s="101" t="inlineStr">
+    <row r="32" spans="1:17" customHeight="1" ht="31.5" s="31" customFormat="1">
+      <c r="A32" s="100" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">위   임   장</t>
           </r>
         </is>
       </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="34"/>
-    </row>
-    <row r="33" spans="1:16144" customHeight="1" ht="17.25" s="32" customFormat="1">
-      <c r="A33" s="102" t="inlineStr">
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="33"/>
+    </row>
+    <row r="33" spans="1:17" customHeight="1" ht="17.25" s="31" customFormat="1">
+      <c r="A33" s="101" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">위 자동차의 말소등록에 따른 모든 행위를 수임자(신청인)에게 위임한다</t>
           </r>
         </is>
       </c>
-      <c r="B33" s="103"/>
-      <c r="C33" s="103"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="103"/>
-      <c r="F33" s="103"/>
-      <c r="G33" s="103"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="103"/>
-      <c r="J33" s="103"/>
-      <c r="K33" s="103"/>
-      <c r="L33" s="103"/>
-      <c r="M33" s="104"/>
-    </row>
-    <row r="34" spans="1:16144" customHeight="1" ht="27" s="32" customFormat="1">
+      <c r="B33" s="102"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="102"/>
+      <c r="E33" s="102"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="102"/>
+      <c r="I33" s="102"/>
+      <c r="J33" s="102"/>
+      <c r="K33" s="102"/>
+      <c r="L33" s="102"/>
+      <c r="M33" s="103"/>
+    </row>
+    <row r="34" spans="1:17" customHeight="1" ht="27" s="31" customFormat="1">
       <c r="A34" s="28" t="inlineStr">
         <is>
           <r>
@@ -2728,14 +2734,14 @@
       <c r="C34" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="105"/>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="105"/>
-      <c r="H34" s="105"/>
-      <c r="I34" s="105"/>
-      <c r="J34" s="105"/>
-      <c r="K34" s="106"/>
+      <c r="D34" s="104"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="104"/>
+      <c r="I34" s="104"/>
+      <c r="J34" s="104"/>
+      <c r="K34" s="105"/>
       <c r="L34" s="30" t="inlineStr">
         <is>
           <r>
@@ -2743,10 +2749,10 @@
           </r>
         </is>
       </c>
-      <c r="M34" s="106"/>
-    </row>
-    <row r="35" spans="1:16144" customHeight="1" ht="27" s="32" customFormat="1">
-      <c r="A35" s="107"/>
+      <c r="M34" s="105"/>
+    </row>
+    <row r="35" spans="1:17" customHeight="1" ht="27" s="31" customFormat="1">
+      <c r="A35" s="106"/>
       <c r="B35" s="8" t="inlineStr">
         <is>
           <r>
@@ -2757,19 +2763,19 @@
       <c r="C35" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="105"/>
-      <c r="E35" s="105"/>
-      <c r="F35" s="105"/>
-      <c r="G35" s="105"/>
-      <c r="H35" s="105"/>
-      <c r="I35" s="105"/>
-      <c r="J35" s="105"/>
-      <c r="K35" s="106"/>
-      <c r="L35" s="108"/>
-      <c r="M35" s="34"/>
-    </row>
-    <row r="36" spans="1:16144" customHeight="1" ht="27" s="32" customFormat="1">
-      <c r="A36" s="109"/>
+      <c r="D35" s="104"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="104"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="104"/>
+      <c r="K35" s="105"/>
+      <c r="L35" s="107"/>
+      <c r="M35" s="33"/>
+    </row>
+    <row r="36" spans="1:17" customHeight="1" ht="27" s="31" customFormat="1">
+      <c r="A36" s="108"/>
       <c r="B36" s="30" t="inlineStr">
         <is>
           <r>
@@ -2777,21 +2783,21 @@
           </r>
         </is>
       </c>
-      <c r="C36" s="110" t="s">
+      <c r="C36" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="105"/>
-      <c r="E36" s="105"/>
-      <c r="F36" s="105"/>
-      <c r="G36" s="105"/>
-      <c r="H36" s="105"/>
-      <c r="I36" s="105"/>
-      <c r="J36" s="105"/>
-      <c r="K36" s="106"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="36"/>
-    </row>
-    <row r="37" spans="1:16144" customHeight="1" ht="30" s="32" customFormat="1">
+      <c r="D36" s="104"/>
+      <c r="E36" s="104"/>
+      <c r="F36" s="104"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="104"/>
+      <c r="I36" s="104"/>
+      <c r="J36" s="104"/>
+      <c r="K36" s="105"/>
+      <c r="L36" s="110"/>
+      <c r="M36" s="35"/>
+    </row>
+    <row r="37" spans="1:17" customHeight="1" ht="30" s="31" customFormat="1">
       <c r="A37" s="28" t="inlineStr">
         <is>
           <r>
@@ -2806,20 +2812,22 @@
           </r>
         </is>
       </c>
-      <c r="C37" s="31"/>
-      <c r="D37" s="105"/>
-      <c r="E37" s="105"/>
-      <c r="F37" s="105"/>
-      <c r="G37" s="105"/>
-      <c r="H37" s="105"/>
-      <c r="I37" s="105"/>
-      <c r="J37" s="105"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="112"/>
-      <c r="M37" s="54"/>
-    </row>
-    <row r="38" spans="1:16144" customHeight="1" ht="30" s="32" customFormat="1">
-      <c r="A38" s="107"/>
+      <c r="C37" s="114" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="104"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="104"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="104"/>
+      <c r="K37" s="105"/>
+      <c r="L37" s="111"/>
+      <c r="M37" s="53"/>
+    </row>
+    <row r="38" spans="1:17" customHeight="1" ht="30" s="31" customFormat="1">
+      <c r="A38" s="106"/>
       <c r="B38" s="8" t="inlineStr">
         <is>
           <r>
@@ -2827,20 +2835,22 @@
           </r>
         </is>
       </c>
-      <c r="C38" s="31"/>
-      <c r="D38" s="105"/>
-      <c r="E38" s="105"/>
-      <c r="F38" s="105"/>
-      <c r="G38" s="105"/>
-      <c r="H38" s="105"/>
-      <c r="I38" s="105"/>
-      <c r="J38" s="105"/>
-      <c r="K38" s="106"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="38"/>
-    </row>
-    <row r="39" spans="1:16144" customHeight="1" ht="30" s="32" customFormat="1">
-      <c r="A39" s="109"/>
+      <c r="C38" s="114" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="104"/>
+      <c r="E38" s="104"/>
+      <c r="F38" s="104"/>
+      <c r="G38" s="104"/>
+      <c r="H38" s="104"/>
+      <c r="I38" s="104"/>
+      <c r="J38" s="104"/>
+      <c r="K38" s="105"/>
+      <c r="L38" s="49"/>
+      <c r="M38" s="37"/>
+    </row>
+    <row r="39" spans="1:17" customHeight="1" ht="30" s="31" customFormat="1">
+      <c r="A39" s="108"/>
       <c r="B39" s="30" t="inlineStr">
         <is>
           <r>
@@ -2848,17 +2858,19 @@
           </r>
         </is>
       </c>
-      <c r="C39" s="113"/>
-      <c r="D39" s="105"/>
-      <c r="E39" s="105"/>
-      <c r="F39" s="105"/>
-      <c r="G39" s="105"/>
-      <c r="H39" s="105"/>
-      <c r="I39" s="105"/>
-      <c r="J39" s="105"/>
-      <c r="K39" s="106"/>
-      <c r="L39" s="114"/>
-      <c r="M39" s="115"/>
+      <c r="C39" s="115" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="104"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="104"/>
+      <c r="G39" s="104"/>
+      <c r="H39" s="104"/>
+      <c r="I39" s="104"/>
+      <c r="J39" s="104"/>
+      <c r="K39" s="105"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="113"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/resources/templates/karaba/deregistration_application.xlsx
+++ b/resources/templates/karaba/deregistration_application.xlsx
@@ -295,7 +295,7 @@
     <t>길영채</t>
   </si>
   <si>
-    <t>11-95-278048-01</t>
+    <t>731110-1041111</t>
   </si>
 </sst>
 </file>
@@ -486,7 +486,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,9 +505,6 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
   </fills>
   <borders count="63">
     <border>
@@ -1630,10 +1627,10 @@
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="60" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="4" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="9" numFmtId="166" fillId="4" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="9" numFmtId="166" fillId="0" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
